--- a/辅助脚本/20260306 易读格式写入json文件/缩略图提取/model_mapping.xlsx
+++ b/辅助脚本/20260306 易读格式写入json文件/缩略图提取/model_mapping.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="109">
   <si>
     <t>VP-BF-180-06</t>
   </si>
@@ -195,9 +195,6 @@
     <t>SW-60X</t>
   </si>
   <si>
-    <t>SZ-80X</t>
-  </si>
-  <si>
     <t>SZ-280XW</t>
   </si>
   <si>
@@ -362,6 +359,13 @@
   </si>
   <si>
     <t>HP-FTB-BF-900-B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VP-BF-180-06U</t>
+  </si>
+  <si>
+    <t>SW-80X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -769,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="35.1" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.375" style="1" customWidth="1"/>
@@ -778,18 +782,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -805,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -821,7 +825,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -837,7 +841,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -853,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -866,10 +870,10 @@
     </row>
     <row r="12" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -882,10 +886,10 @@
     </row>
     <row r="14" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -893,7 +897,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -901,7 +905,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -909,7 +913,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -917,7 +921,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -954,10 +958,10 @@
     </row>
     <row r="23" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -986,10 +990,10 @@
     </row>
     <row r="27" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -1018,7 +1022,7 @@
     </row>
     <row r="31" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>36</v>
@@ -1026,7 +1030,7 @@
     </row>
     <row r="32" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>37</v>
@@ -1034,7 +1038,7 @@
     </row>
     <row r="33" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>36</v>
@@ -1050,7 +1054,7 @@
     </row>
     <row r="35" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>40</v>
@@ -1066,7 +1070,7 @@
     </row>
     <row r="37" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>43</v>
@@ -1082,7 +1086,7 @@
     </row>
     <row r="39" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>46</v>
@@ -1090,15 +1094,15 @@
     </row>
     <row r="40" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>47</v>
@@ -1106,7 +1110,7 @@
     </row>
     <row r="42" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>48</v>
@@ -1122,7 +1126,7 @@
     </row>
     <row r="44" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>50</v>
@@ -1130,10 +1134,10 @@
     </row>
     <row r="45" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -1146,7 +1150,7 @@
     </row>
     <row r="47" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>53</v>
@@ -1154,7 +1158,7 @@
     </row>
     <row r="48" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>54</v>
@@ -1162,7 +1166,7 @@
     </row>
     <row r="49" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>55</v>
@@ -1170,7 +1174,7 @@
     </row>
     <row r="50" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>56</v>
@@ -1178,66 +1182,74 @@
     </row>
     <row r="51" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>58</v>
+      <c r="A52" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>63</v>
+      <c r="B59" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
